--- a/artfynd/A 48069-2023 artfynd.xlsx
+++ b/artfynd/A 48069-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132572793</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48069-2023 artfynd.xlsx
+++ b/artfynd/A 48069-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132572793</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48069-2023 artfynd.xlsx
+++ b/artfynd/A 48069-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Sundin, Eva Sundin</t>
+          <t>Eva Sundin, Håkan Sundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 48069-2023 artfynd.xlsx
+++ b/artfynd/A 48069-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132572793</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>57865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Sundin, Håkan Sundin</t>
+          <t>Håkan Sundin, Eva Sundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
